--- a/artfynd/A 48899-2024 artfynd.xlsx
+++ b/artfynd/A 48899-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109181619</v>
+        <v>114139641</v>
       </c>
       <c r="B2" t="n">
-        <v>98972</v>
+        <v>100815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,24 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>219851</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Hässlebrodd</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Milium effusum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>900 m N om vägförgrening O om Norr-Lillån, Nb</t>
@@ -759,12 +763,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>rikt, fuktigt vägdike</t>
+          <t>rik ungskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,6 +784,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109181619</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>900 m N om vägförgrening O om Norr-Lillån, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>790395</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7369848</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2008-06-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2008-06-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>rikt, fuktigt vägdike</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>jan Ahlm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
         </is>

--- a/artfynd/A 48899-2024 artfynd.xlsx
+++ b/artfynd/A 48899-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114139641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,8 +909,17 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109181619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>